--- a/data/TDS.xlsx
+++ b/data/TDS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Projects\hindcon-product-assistant\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -2916,14 +2916,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2969,16 +2966,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2987,6 +2975,21 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3272,26 +3275,26 @@
   <dimension ref="A1:E321"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" style="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="84.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="28" customFormat="1">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:5" s="25" customFormat="1">
+      <c r="A1" s="25" t="s">
         <v>575</v>
       </c>
       <c r="B1" s="29" t="s">
         <v>896</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="26" t="s">
         <v>897</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="27" t="s">
         <v>898</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="28" t="s">
         <v>899</v>
       </c>
     </row>
@@ -3299,121 +3302,121 @@
       <c r="A2" t="s">
         <v>576</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>577</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>578</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>579</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>580</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>581</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>582</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>583</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3421,91 +3424,91 @@
       <c r="A10" t="s">
         <v>584</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>585</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>586</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>587</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>588</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>589</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3513,211 +3516,211 @@
       <c r="A16" t="s">
         <v>590</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>591</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>592</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>593</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>594</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>595</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>596</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>597</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>598</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>599</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>600</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>601</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>602</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>603</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3725,76 +3728,76 @@
       <c r="A30" t="s">
         <v>604</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>605</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>606</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>607</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>608</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="6" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3802,16 +3805,16 @@
       <c r="A35" t="s">
         <v>609</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3819,16 +3822,16 @@
       <c r="A36" t="s">
         <v>610</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3836,22 +3839,22 @@
       <c r="A37" t="s">
         <v>611</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="8"/>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>612</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3866,7 +3869,7 @@
       <c r="A39" t="s">
         <v>613</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3881,7 +3884,7 @@
       <c r="A40" t="s">
         <v>614</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3896,7 +3899,7 @@
       <c r="A41" t="s">
         <v>615</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3911,7 +3914,7 @@
       <c r="A42" t="s">
         <v>616</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3926,7 +3929,7 @@
       <c r="A43" t="s">
         <v>617</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -3941,7 +3944,7 @@
       <c r="A44" t="s">
         <v>618</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -3956,7 +3959,7 @@
       <c r="A45" t="s">
         <v>619</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -3971,7 +3974,7 @@
       <c r="A46" t="s">
         <v>620</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -3988,7 +3991,7 @@
       <c r="A47" t="s">
         <v>621</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -4003,7 +4006,7 @@
       <c r="A48" t="s">
         <v>622</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -4018,7 +4021,7 @@
       <c r="A49" t="s">
         <v>623</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -4033,7 +4036,7 @@
       <c r="A50" t="s">
         <v>624</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -4048,7 +4051,7 @@
       <c r="A51" t="s">
         <v>625</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -4063,7 +4066,7 @@
       <c r="A52" t="s">
         <v>626</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -4080,7 +4083,7 @@
       <c r="A53" t="s">
         <v>627</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -4095,7 +4098,7 @@
       <c r="A54" t="s">
         <v>628</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -4110,7 +4113,7 @@
       <c r="A55" t="s">
         <v>629</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -4125,7 +4128,7 @@
       <c r="A56" t="s">
         <v>630</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -4140,151 +4143,151 @@
       <c r="A57" t="s">
         <v>631</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E57" s="8"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>632</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E58" s="8"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>633</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E59" s="8"/>
+      <c r="E59" s="7"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>634</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E60" s="8"/>
+      <c r="E60" s="7"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>635</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E61" s="8"/>
+      <c r="E61" s="7"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>636</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="8"/>
+      <c r="E62" s="7"/>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>637</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E63" s="8"/>
+      <c r="E63" s="7"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>638</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E64" s="8"/>
+      <c r="E64" s="7"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>639</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E65" s="8"/>
+      <c r="E65" s="7"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>640</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="6" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4292,61 +4295,61 @@
       <c r="A67" t="s">
         <v>641</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="8"/>
+      <c r="E67" s="7"/>
     </row>
     <row r="68" spans="1:5" ht="26.25">
       <c r="A68" t="s">
         <v>642</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E68" s="8"/>
+      <c r="E68" s="7"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>643</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E69" s="8"/>
+      <c r="E69" s="7"/>
     </row>
     <row r="70" spans="1:5" ht="26.25">
       <c r="A70" t="s">
         <v>644</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4354,59 +4357,59 @@
       <c r="A71" t="s">
         <v>645</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="8"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="7"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>646</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E72" s="8"/>
+      <c r="E72" s="7"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>647</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E73" s="8"/>
+      <c r="E73" s="7"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>648</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E74" s="15" t="s">
         <v>280</v>
       </c>
     </row>
@@ -4414,217 +4417,217 @@
       <c r="A75" t="s">
         <v>649</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E75" s="8"/>
+      <c r="E75" s="7"/>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>650</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="E76" s="8"/>
+      <c r="E76" s="7"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>651</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E77" s="8"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>652</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E78" s="8"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>653</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E79" s="8"/>
+      <c r="E79" s="7"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>654</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E80" s="8"/>
+      <c r="E80" s="7"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>655</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="E81" s="8"/>
+      <c r="E81" s="7"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>656</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="E82" s="8"/>
+      <c r="E82" s="7"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>657</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E83" s="8"/>
+      <c r="E83" s="7"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>658</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E84" s="8"/>
+      <c r="E84" s="7"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>659</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E85" s="8"/>
+      <c r="E85" s="7"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>660</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E86" s="8"/>
+      <c r="E86" s="7"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>661</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E87" s="8"/>
+      <c r="E87" s="7"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>662</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C88" s="17" t="s">
+      <c r="C88" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E88" s="8"/>
+      <c r="E88" s="7"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>663</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -4638,7 +4641,7 @@
       <c r="A90" t="s">
         <v>664</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -4652,7 +4655,7 @@
       <c r="A91" t="s">
         <v>665</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -4666,7 +4669,7 @@
       <c r="A92" t="s">
         <v>666</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C92" s="2" t="s">
@@ -4680,7 +4683,7 @@
       <c r="A93" t="s">
         <v>667</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -4694,7 +4697,7 @@
       <c r="A94" t="s">
         <v>668</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -4708,7 +4711,7 @@
       <c r="A95" t="s">
         <v>669</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="33" t="s">
         <v>45</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -4722,31 +4725,31 @@
       <c r="A96" t="s">
         <v>670</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="E96" s="8"/>
+      <c r="E96" s="7"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>671</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C97" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="E97" s="16" t="s">
+      <c r="E97" s="15" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4754,256 +4757,256 @@
       <c r="A98" t="s">
         <v>672</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="E98" s="8"/>
+      <c r="E98" s="7"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>673</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C99" s="9" t="s">
+      <c r="C99" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E99" s="8"/>
+      <c r="E99" s="7"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>674</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E100" s="8"/>
+      <c r="E100" s="7"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>675</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E101" s="8"/>
+      <c r="E101" s="7"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>676</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="E102" s="8"/>
+      <c r="E102" s="7"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>677</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E103" s="8"/>
+      <c r="E103" s="7"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>678</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C104" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="E104" s="8"/>
+      <c r="E104" s="7"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>679</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C105" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E105" s="8"/>
+      <c r="E105" s="7"/>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>680</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C106" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E106" s="8"/>
+      <c r="E106" s="7"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>681</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C107" s="9" t="s">
+      <c r="C107" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E107" s="8"/>
+      <c r="E107" s="7"/>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>682</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E108" s="8"/>
+      <c r="E108" s="7"/>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>683</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C109" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E109" s="8"/>
+      <c r="E109" s="7"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>684</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E110" s="8"/>
+      <c r="E110" s="7"/>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>685</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E111" s="8"/>
+      <c r="E111" s="7"/>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>686</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E112" s="8"/>
+      <c r="E112" s="7"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>687</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C113" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E113" s="8"/>
+      <c r="E113" s="7"/>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>688</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="6" t="s">
         <v>346</v>
       </c>
     </row>
@@ -5011,31 +5014,31 @@
       <c r="A115" t="s">
         <v>689</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C115" s="9" t="s">
+      <c r="C115" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E115" s="8"/>
+      <c r="E115" s="7"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>690</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C116" s="9" t="s">
+      <c r="C116" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="E116" s="6" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5043,91 +5046,91 @@
       <c r="A117" t="s">
         <v>691</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C117" s="9" t="s">
+      <c r="C117" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E117" s="11"/>
+      <c r="E117" s="10"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>692</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C118" s="9" t="s">
+      <c r="C118" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E118" s="8"/>
+      <c r="E118" s="7"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>693</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="C119" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D119" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="E119" s="8"/>
+      <c r="E119" s="7"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>694</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="C120" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="E120" s="8"/>
+      <c r="E120" s="7"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>695</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C121" s="9" t="s">
+      <c r="C121" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="D121" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="E121" s="8"/>
+      <c r="E121" s="7"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>696</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C122" s="9" t="s">
+      <c r="C122" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="6" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5135,346 +5138,346 @@
       <c r="A123" t="s">
         <v>697</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="D123" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E123" s="8"/>
+      <c r="E123" s="7"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>698</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C124" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="D124" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="E124" s="8"/>
+      <c r="E124" s="7"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>699</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D125" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E125" s="8"/>
+      <c r="E125" s="7"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>700</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="E126" s="8"/>
+      <c r="E126" s="7"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>701</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="D127" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E127" s="8"/>
+      <c r="E127" s="7"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>702</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="D128" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="E128" s="8"/>
+      <c r="E128" s="7"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>703</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C129" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="D129" s="7" t="s">
+      <c r="D129" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="E129" s="8"/>
+      <c r="E129" s="7"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>704</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="D130" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E130" s="8"/>
+      <c r="E130" s="7"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>705</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="D131" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="E131" s="8"/>
+      <c r="E131" s="7"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>706</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="D132" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="E132" s="8"/>
+      <c r="E132" s="7"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>707</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="D133" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="E133" s="8"/>
+      <c r="E133" s="7"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>708</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="D134" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="E134" s="8"/>
+      <c r="E134" s="7"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>709</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="D135" s="7" t="s">
+      <c r="D135" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="E135" s="8"/>
+      <c r="E135" s="7"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>710</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="D136" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="E136" s="8"/>
+      <c r="E136" s="7"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>711</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C137" s="9" t="s">
+      <c r="C137" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="D137" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="E137" s="8"/>
+      <c r="E137" s="7"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>712</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="E138" s="8"/>
+      <c r="E138" s="7"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>713</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="D139" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="E139" s="8"/>
+      <c r="E139" s="7"/>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>714</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="E140" s="8"/>
+      <c r="E140" s="7"/>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>715</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="D141" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="E141" s="8"/>
+      <c r="E141" s="7"/>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>716</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="E142" s="8"/>
+      <c r="E142" s="7"/>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>717</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E143" s="8"/>
+      <c r="E143" s="7"/>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>718</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="E144" s="8"/>
+      <c r="E144" s="7"/>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>719</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C145" s="18" t="s">
+      <c r="C145" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="6" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5482,151 +5485,151 @@
       <c r="A146" t="s">
         <v>720</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="E146" s="8"/>
+      <c r="E146" s="7"/>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>721</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="E147" s="8"/>
+      <c r="E147" s="7"/>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>722</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="D148" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="E148" s="8"/>
+      <c r="E148" s="7"/>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>723</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="E149" s="8"/>
+      <c r="E149" s="7"/>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>724</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="E150" s="8"/>
+      <c r="E150" s="7"/>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>725</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="D151" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="E151" s="8"/>
+      <c r="E151" s="7"/>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>726</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C152" s="9" t="s">
+      <c r="C152" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D152" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="E152" s="8"/>
+      <c r="E152" s="7"/>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>727</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C153" s="9" t="s">
+      <c r="C153" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="E153" s="8"/>
+      <c r="E153" s="7"/>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>728</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C154" s="9" t="s">
+      <c r="C154" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E154" s="8"/>
+      <c r="E154" s="7"/>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>729</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C155" s="9" t="s">
+      <c r="C155" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="D155" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" s="6" t="s">
         <v>431</v>
       </c>
     </row>
@@ -5634,67 +5637,67 @@
       <c r="A156" t="s">
         <v>730</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C156" s="9" t="s">
+      <c r="C156" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E156" s="8"/>
+      <c r="E156" s="7"/>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>731</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="E157" s="8"/>
+      <c r="E157" s="7"/>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>732</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C158" s="9" t="s">
+      <c r="C158" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="E158" s="8"/>
+      <c r="E158" s="7"/>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>733</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C159" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="D159" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="E159" s="8"/>
+      <c r="E159" s="7"/>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>734</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="32" t="s">
         <v>54</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -5708,337 +5711,337 @@
       <c r="A161" t="s">
         <v>735</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C161" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="D161" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="E161" s="8"/>
+      <c r="E161" s="7"/>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
         <v>736</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C162" s="9" t="s">
+      <c r="C162" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="E162" s="8"/>
+      <c r="E162" s="7"/>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>737</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C163" s="9" t="s">
+      <c r="C163" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D163" s="7" t="s">
+      <c r="D163" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E163" s="8"/>
+      <c r="E163" s="7"/>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
         <v>738</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C164" s="9" t="s">
+      <c r="C164" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D164" s="7" t="s">
+      <c r="D164" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="E164" s="8"/>
+      <c r="E164" s="7"/>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>739</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C165" s="9" t="s">
+      <c r="C165" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="D165" s="7" t="s">
+      <c r="D165" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="E165" s="8"/>
+      <c r="E165" s="7"/>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>740</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C166" s="9" t="s">
+      <c r="C166" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="E166" s="8"/>
+      <c r="E166" s="7"/>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>741</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C167" s="9" t="s">
+      <c r="C167" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="D167" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="E167" s="8"/>
+      <c r="E167" s="7"/>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>742</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C168" s="9" t="s">
+      <c r="C168" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="D168" s="7" t="s">
+      <c r="D168" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="E168" s="8"/>
+      <c r="E168" s="7"/>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>743</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C169" s="9" t="s">
+      <c r="C169" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="D169" s="7" t="s">
+      <c r="D169" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="E169" s="8"/>
+      <c r="E169" s="7"/>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>744</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C170" s="9" t="s">
+      <c r="C170" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="D170" s="7" t="s">
+      <c r="D170" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="E170" s="8"/>
+      <c r="E170" s="7"/>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>745</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C171" s="9" t="s">
+      <c r="C171" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="D171" s="7" t="s">
+      <c r="D171" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="E171" s="8"/>
+      <c r="E171" s="7"/>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>746</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C172" s="9" t="s">
+      <c r="C172" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D172" s="7" t="s">
+      <c r="D172" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="E172" s="8"/>
+      <c r="E172" s="7"/>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>747</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C173" s="9" t="s">
+      <c r="C173" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="D173" s="7" t="s">
+      <c r="D173" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="E173" s="8"/>
+      <c r="E173" s="7"/>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>748</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C174" s="9" t="s">
+      <c r="C174" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="D174" s="7" t="s">
+      <c r="D174" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="E174" s="8"/>
+      <c r="E174" s="7"/>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>749</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C175" s="9" t="s">
+      <c r="C175" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="D175" s="7" t="s">
+      <c r="D175" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="E175" s="8"/>
+      <c r="E175" s="7"/>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>750</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C176" s="14" t="s">
+      <c r="C176" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="D176" s="7" t="s">
+      <c r="D176" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="E176" s="8"/>
+      <c r="E176" s="7"/>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>751</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C177" s="9" t="s">
+      <c r="C177" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="D177" s="7" t="s">
+      <c r="D177" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="E177" s="8"/>
+      <c r="E177" s="7"/>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>752</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C178" s="9" t="s">
+      <c r="C178" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="D178" s="7" t="s">
+      <c r="D178" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="E178" s="8"/>
+      <c r="E178" s="7"/>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>753</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C179" s="9" t="s">
+      <c r="C179" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="D179" s="7" t="s">
+      <c r="D179" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="E179" s="8"/>
+      <c r="E179" s="7"/>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>754</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C180" s="9" t="s">
+      <c r="C180" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="D180" s="7" t="s">
+      <c r="D180" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="E180" s="8"/>
+      <c r="E180" s="7"/>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>755</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C181" s="9" t="s">
+      <c r="C181" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="D181" s="7" t="s">
+      <c r="D181" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="E181" s="8"/>
+      <c r="E181" s="7"/>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>756</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C182" s="9" t="s">
+      <c r="C182" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="D182" s="7" t="s">
+      <c r="D182" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E182" s="8"/>
+      <c r="E182" s="7"/>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>757</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="32" t="s">
         <v>57</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -6053,223 +6056,223 @@
       <c r="A184" t="s">
         <v>758</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C184" s="19" t="s">
+      <c r="C184" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="D184" s="7" t="s">
+      <c r="D184" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="E184" s="8"/>
+      <c r="E184" s="7"/>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>759</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C185" s="19" t="s">
+      <c r="C185" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="D185" s="7" t="s">
+      <c r="D185" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="E185" s="8"/>
+      <c r="E185" s="7"/>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>760</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C186" s="19" t="s">
+      <c r="C186" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="D186" s="7" t="s">
+      <c r="D186" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="E186" s="8"/>
+      <c r="E186" s="7"/>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>761</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C187" s="19" t="s">
+      <c r="C187" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="D187" s="7" t="s">
+      <c r="D187" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="E187" s="8"/>
+      <c r="E187" s="7"/>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>762</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C188" s="19" t="s">
+      <c r="C188" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="D188" s="7" t="s">
+      <c r="D188" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="E188" s="8"/>
+      <c r="E188" s="7"/>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>763</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C189" s="19" t="s">
+      <c r="C189" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="D189" s="7" t="s">
+      <c r="D189" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="E189" s="8"/>
+      <c r="E189" s="7"/>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
         <v>764</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C190" s="19" t="s">
+      <c r="C190" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="D190" s="7" t="s">
+      <c r="D190" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="E190" s="8"/>
+      <c r="E190" s="7"/>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
         <v>765</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C191" s="19" t="s">
+      <c r="C191" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="D191" s="7" t="s">
+      <c r="D191" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="E191" s="8"/>
+      <c r="E191" s="7"/>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
         <v>766</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C192" s="19" t="s">
+      <c r="C192" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="D192" s="7" t="s">
+      <c r="D192" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="E192" s="8"/>
+      <c r="E192" s="7"/>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
         <v>767</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="C193" s="19" t="s">
+      <c r="C193" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="D193" s="7" t="s">
+      <c r="D193" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="E193" s="8"/>
+      <c r="E193" s="7"/>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
         <v>768</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="33" t="s">
         <v>568</v>
       </c>
-      <c r="C194" s="20" t="s">
+      <c r="C194" s="19" t="s">
         <v>504</v>
       </c>
-      <c r="D194" s="7" t="s">
+      <c r="D194" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="E194" s="8"/>
+      <c r="E194" s="7"/>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
         <v>769</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="33" t="s">
         <v>568</v>
       </c>
-      <c r="C195" s="20" t="s">
+      <c r="C195" s="19" t="s">
         <v>506</v>
       </c>
-      <c r="D195" s="7" t="s">
+      <c r="D195" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="E195" s="8"/>
+      <c r="E195" s="7"/>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
         <v>770</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="33" t="s">
         <v>568</v>
       </c>
-      <c r="C196" s="20" t="s">
+      <c r="C196" s="19" t="s">
         <v>508</v>
       </c>
-      <c r="D196" s="7" t="s">
+      <c r="D196" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E196" s="8"/>
+      <c r="E196" s="7"/>
     </row>
     <row r="197" spans="1:5" ht="29.25">
       <c r="A197" t="s">
         <v>771</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="33" t="s">
         <v>568</v>
       </c>
-      <c r="C197" s="21" t="s">
+      <c r="C197" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="D197" s="7" t="s">
+      <c r="D197" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="E197" s="8"/>
+      <c r="E197" s="7"/>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
         <v>772</v>
       </c>
-      <c r="B198" s="27" t="s">
+      <c r="B198" s="30" t="s">
         <v>512</v>
       </c>
-      <c r="C198" s="19" t="s">
+      <c r="C198" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="D198" s="7" t="s">
+      <c r="D198" s="6" t="s">
         <v>514</v>
       </c>
     </row>
@@ -6277,13 +6280,13 @@
       <c r="A199" t="s">
         <v>773</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="33" t="s">
         <v>569</v>
       </c>
-      <c r="C199" s="13" t="s">
+      <c r="C199" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D199" s="7" t="s">
+      <c r="D199" s="6" t="s">
         <v>515</v>
       </c>
     </row>
@@ -6291,13 +6294,13 @@
       <c r="A200" t="s">
         <v>774</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="33" t="s">
         <v>569</v>
       </c>
-      <c r="C200" s="13" t="s">
+      <c r="C200" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="D200" s="7" t="s">
+      <c r="D200" s="6" t="s">
         <v>516</v>
       </c>
     </row>
@@ -6305,13 +6308,13 @@
       <c r="A201" t="s">
         <v>775</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="33" t="s">
         <v>569</v>
       </c>
-      <c r="C201" s="13" t="s">
+      <c r="C201" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="D201" s="7" t="s">
+      <c r="D201" s="6" t="s">
         <v>518</v>
       </c>
     </row>
@@ -6324,204 +6327,204 @@
       <c r="A203" t="s">
         <v>777</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="33" t="s">
         <v>570</v>
       </c>
-      <c r="C203" s="9" t="s">
+      <c r="C203" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="D203" s="7" t="s">
+      <c r="D203" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="E203" s="8"/>
+      <c r="E203" s="7"/>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
         <v>778</v>
       </c>
-      <c r="C204" s="9"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="7"/>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
         <v>779</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C205" s="9" t="s">
+      <c r="C205" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D205" s="7" t="s">
+      <c r="D205" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="E205" s="8"/>
+      <c r="E205" s="7"/>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
         <v>780</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C206" s="9" t="s">
+      <c r="C206" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="D206" s="7" t="s">
+      <c r="D206" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="E206" s="8"/>
+      <c r="E206" s="7"/>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
         <v>781</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C207" s="9" t="s">
+      <c r="C207" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D207" s="7" t="s">
+      <c r="D207" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="E207" s="8"/>
+      <c r="E207" s="7"/>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
         <v>782</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C208" s="9" t="s">
+      <c r="C208" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="D208" s="7" t="s">
+      <c r="D208" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="E208" s="8"/>
+      <c r="E208" s="7"/>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
         <v>783</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="C209" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="D209" s="7" t="s">
+      <c r="D209" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E209" s="8"/>
+      <c r="E209" s="7"/>
     </row>
     <row r="210" spans="1:5" ht="26.25">
       <c r="A210" t="s">
         <v>784</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C210" s="14" t="s">
+      <c r="C210" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="D210" s="7" t="s">
+      <c r="D210" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="E210" s="8"/>
+      <c r="E210" s="7"/>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
         <v>785</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C211" s="9" t="s">
+      <c r="C211" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D211" s="7" t="s">
+      <c r="D211" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E211" s="8"/>
+      <c r="E211" s="7"/>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>786</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C212" s="9" t="s">
+      <c r="C212" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="D212" s="7" t="s">
+      <c r="D212" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="E212" s="8"/>
+      <c r="E212" s="7"/>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
         <v>787</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C213" s="9" t="s">
+      <c r="C213" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D213" s="7" t="s">
+      <c r="D213" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E213" s="8"/>
+      <c r="E213" s="7"/>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
         <v>788</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C214" s="9" t="s">
+      <c r="C214" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D214" s="7" t="s">
+      <c r="D214" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="E214" s="8"/>
+      <c r="E214" s="7"/>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
         <v>789</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C215" s="9" t="s">
+      <c r="C215" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D215" s="7" t="s">
+      <c r="D215" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E215" s="8"/>
+      <c r="E215" s="7"/>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
         <v>790</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="C216" s="9" t="s">
+      <c r="C216" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="D216" s="7" t="s">
+      <c r="D216" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="E216" s="8"/>
+      <c r="E216" s="7"/>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
@@ -6532,16 +6535,16 @@
       <c r="A218" t="s">
         <v>792</v>
       </c>
-      <c r="B218" s="26" t="s">
+      <c r="B218" s="31" t="s">
         <v>532</v>
       </c>
-      <c r="C218" s="9" t="s">
+      <c r="C218" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="D218" s="7" t="s">
+      <c r="D218" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="E218" s="8"/>
+      <c r="E218" s="7"/>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
@@ -6552,13 +6555,13 @@
       <c r="A220" t="s">
         <v>794</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="33" t="s">
         <v>572</v>
       </c>
-      <c r="C220" s="9" t="s">
+      <c r="C220" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="D220" s="7" t="s">
+      <c r="D220" s="6" t="s">
         <v>536</v>
       </c>
     </row>
@@ -6566,13 +6569,13 @@
       <c r="A221" t="s">
         <v>795</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="33" t="s">
         <v>572</v>
       </c>
-      <c r="C221" s="9" t="s">
+      <c r="C221" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="D221" s="7" t="s">
+      <c r="D221" s="6" t="s">
         <v>538</v>
       </c>
     </row>
@@ -6580,7 +6583,7 @@
       <c r="A222" t="s">
         <v>796</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="33" t="s">
         <v>572</v>
       </c>
     </row>
@@ -6588,16 +6591,16 @@
       <c r="A223" t="s">
         <v>797</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C223" s="22" t="s">
+      <c r="C223" s="21" t="s">
         <v>539</v>
       </c>
-      <c r="D223" s="23" t="s">
+      <c r="D223" s="22" t="s">
         <v>540</v>
       </c>
-      <c r="E223" s="7" t="s">
+      <c r="E223" s="6" t="s">
         <v>541</v>
       </c>
     </row>
@@ -6605,76 +6608,76 @@
       <c r="A224" t="s">
         <v>798</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C224" s="22" t="s">
+      <c r="C224" s="21" t="s">
         <v>542</v>
       </c>
-      <c r="D224" s="7" t="s">
+      <c r="D224" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="E224" s="8"/>
+      <c r="E224" s="7"/>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
         <v>799</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C225" s="22" t="s">
+      <c r="C225" s="21" t="s">
         <v>544</v>
       </c>
-      <c r="D225" s="7" t="s">
+      <c r="D225" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E225" s="8"/>
+      <c r="E225" s="7"/>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
         <v>800</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C226" s="22" t="s">
+      <c r="C226" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="D226" s="7" t="s">
+      <c r="D226" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="E226" s="8"/>
+      <c r="E226" s="7"/>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
         <v>801</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C227" s="22" t="s">
+      <c r="C227" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="D227" s="7" t="s">
+      <c r="D227" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="E227" s="8"/>
+      <c r="E227" s="7"/>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
         <v>802</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="33" t="s">
         <v>573</v>
       </c>
-      <c r="C228" s="22" t="s">
+      <c r="C228" s="21" t="s">
         <v>550</v>
       </c>
-      <c r="D228" s="7" t="s">
+      <c r="D228" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="E228" s="8"/>
+      <c r="E228" s="7"/>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
@@ -6685,121 +6688,121 @@
       <c r="A230" t="s">
         <v>804</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C230" s="24" t="s">
+      <c r="C230" s="23" t="s">
         <v>552</v>
       </c>
-      <c r="D230" s="25" t="s">
+      <c r="D230" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E230" s="8"/>
+      <c r="E230" s="7"/>
     </row>
     <row r="231" spans="1:5" ht="26.25">
       <c r="A231" t="s">
         <v>805</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C231" s="24" t="s">
+      <c r="C231" s="23" t="s">
         <v>554</v>
       </c>
-      <c r="D231" s="25" t="s">
+      <c r="D231" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E231" s="8"/>
+      <c r="E231" s="7"/>
     </row>
     <row r="232" spans="1:5" ht="26.25">
       <c r="A232" t="s">
         <v>806</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C232" s="24" t="s">
+      <c r="C232" s="23" t="s">
         <v>555</v>
       </c>
-      <c r="D232" s="25" t="s">
+      <c r="D232" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E232" s="8"/>
+      <c r="E232" s="7"/>
     </row>
     <row r="233" spans="1:5" ht="26.25">
       <c r="A233" t="s">
         <v>807</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C233" s="24" t="s">
+      <c r="C233" s="23" t="s">
         <v>556</v>
       </c>
-      <c r="D233" s="25" t="s">
+      <c r="D233" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E233" s="8"/>
+      <c r="E233" s="7"/>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
         <v>808</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C234" s="22" t="s">
+      <c r="C234" s="21" t="s">
         <v>557</v>
       </c>
-      <c r="D234" s="25" t="s">
+      <c r="D234" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E234" s="8"/>
+      <c r="E234" s="7"/>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
         <v>809</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C235" s="22" t="s">
+      <c r="C235" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="D235" s="25" t="s">
+      <c r="D235" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E235" s="8"/>
+      <c r="E235" s="7"/>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
         <v>810</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C236" s="22" t="s">
+      <c r="C236" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="D236" s="7" t="s">
+      <c r="D236" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="E236" s="8"/>
+      <c r="E236" s="7"/>
     </row>
     <row r="237" spans="1:5" ht="26.25">
       <c r="A237" t="s">
         <v>811</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="C237" s="24" t="s">
+      <c r="C237" s="23" t="s">
         <v>561</v>
       </c>
-      <c r="D237" s="7" t="s">
+      <c r="D237" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="E237" s="7" t="s">
+      <c r="E237" s="6" t="s">
         <v>563</v>
       </c>
     </row>
@@ -6807,10 +6810,10 @@
       <c r="A238" t="s">
         <v>812</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C238" s="5" t="s">
+      <c r="C238" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D238" s="3" t="s">
@@ -6822,7 +6825,7 @@
       <c r="A239" t="s">
         <v>813</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -6837,7 +6840,7 @@
       <c r="A240" t="s">
         <v>814</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -6852,7 +6855,7 @@
       <c r="A241" t="s">
         <v>815</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C241" s="2" t="s">
@@ -6867,7 +6870,7 @@
       <c r="A242" t="s">
         <v>816</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -6882,7 +6885,7 @@
       <c r="A243" t="s">
         <v>817</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B243" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -6897,7 +6900,7 @@
       <c r="A244" t="s">
         <v>818</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="32" t="s">
         <v>66</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -6912,391 +6915,391 @@
       <c r="A245" t="s">
         <v>819</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C245" s="9" t="s">
+      <c r="C245" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D245" s="7" t="s">
+      <c r="D245" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E245" s="8"/>
+      <c r="E245" s="7"/>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
         <v>820</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C246" s="9" t="s">
+      <c r="C246" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D246" s="7" t="s">
+      <c r="D246" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E246" s="8"/>
+      <c r="E246" s="7"/>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
         <v>821</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C247" s="9" t="s">
+      <c r="C247" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D247" s="7" t="s">
+      <c r="D247" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E247" s="8"/>
+      <c r="E247" s="7"/>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
         <v>822</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C248" s="9" t="s">
+      <c r="C248" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D248" s="7" t="s">
+      <c r="D248" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E248" s="8"/>
+      <c r="E248" s="7"/>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
         <v>823</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C249" s="9" t="s">
+      <c r="C249" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D249" s="7" t="s">
+      <c r="D249" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E249" s="8"/>
+      <c r="E249" s="7"/>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
         <v>824</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C250" s="9" t="s">
+      <c r="C250" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D250" s="7" t="s">
+      <c r="D250" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E250" s="8"/>
+      <c r="E250" s="7"/>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
         <v>825</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C251" s="9" t="s">
+      <c r="C251" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D251" s="7" t="s">
+      <c r="D251" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E251" s="8"/>
+      <c r="E251" s="7"/>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
         <v>826</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C252" s="9" t="s">
+      <c r="C252" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D252" s="7" t="s">
+      <c r="D252" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E252" s="8"/>
+      <c r="E252" s="7"/>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
         <v>827</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C253" s="9" t="s">
+      <c r="C253" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D253" s="7" t="s">
+      <c r="D253" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E253" s="8"/>
+      <c r="E253" s="7"/>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
         <v>828</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C254" s="9" t="s">
+      <c r="C254" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D254" s="7" t="s">
+      <c r="D254" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E254" s="8"/>
+      <c r="E254" s="7"/>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
         <v>829</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C255" s="9" t="s">
+      <c r="C255" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D255" s="7" t="s">
+      <c r="D255" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E255" s="10"/>
+      <c r="E255" s="9"/>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
         <v>830</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C256" s="9" t="s">
+      <c r="C256" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D256" s="7" t="s">
+      <c r="D256" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E256" s="10"/>
+      <c r="E256" s="9"/>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
         <v>831</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C257" s="9" t="s">
+      <c r="C257" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D257" s="7" t="s">
+      <c r="D257" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E257" s="8"/>
+      <c r="E257" s="7"/>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
         <v>832</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C258" s="9" t="s">
+      <c r="C258" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D258" s="7" t="s">
+      <c r="D258" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E258" s="8"/>
+      <c r="E258" s="7"/>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
         <v>833</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C259" s="9" t="s">
+      <c r="C259" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D259" s="7" t="s">
+      <c r="D259" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E259" s="8"/>
+      <c r="E259" s="7"/>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
         <v>834</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C260" s="9" t="s">
+      <c r="C260" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D260" s="7" t="s">
+      <c r="D260" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E260" s="8"/>
+      <c r="E260" s="7"/>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
         <v>835</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C261" s="9" t="s">
+      <c r="C261" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D261" s="7" t="s">
+      <c r="D261" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E261" s="8"/>
+      <c r="E261" s="7"/>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
         <v>836</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C262" s="9" t="s">
+      <c r="C262" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D262" s="7" t="s">
+      <c r="D262" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E262" s="8"/>
+      <c r="E262" s="7"/>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
         <v>837</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C263" s="9" t="s">
+      <c r="C263" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D263" s="7" t="s">
+      <c r="D263" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E263" s="8"/>
+      <c r="E263" s="7"/>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
         <v>838</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C264" s="9" t="s">
+      <c r="C264" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D264" s="7" t="s">
+      <c r="D264" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E264" s="8"/>
+      <c r="E264" s="7"/>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
         <v>839</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C265" s="9" t="s">
+      <c r="C265" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D265" s="7" t="s">
+      <c r="D265" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E265" s="8"/>
+      <c r="E265" s="7"/>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
         <v>840</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C266" s="9" t="s">
+      <c r="C266" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D266" s="7" t="s">
+      <c r="D266" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E266" s="8"/>
+      <c r="E266" s="7"/>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
         <v>841</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C267" s="9" t="s">
+      <c r="C267" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D267" s="7" t="s">
+      <c r="D267" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E267" s="8"/>
+      <c r="E267" s="7"/>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
         <v>842</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C268" s="9" t="s">
+      <c r="C268" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D268" s="7" t="s">
+      <c r="D268" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E268" s="8"/>
+      <c r="E268" s="7"/>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
         <v>843</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C269" s="9" t="s">
+      <c r="C269" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D269" s="7" t="s">
+      <c r="D269" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E269" s="8"/>
+      <c r="E269" s="7"/>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
         <v>844</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C270" s="9" t="s">
+      <c r="C270" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="D270" s="7" t="s">
+      <c r="D270" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E270" s="7" t="s">
+      <c r="E270" s="6" t="s">
         <v>209</v>
       </c>
     </row>
@@ -7304,406 +7307,406 @@
       <c r="A271" t="s">
         <v>845</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C271" s="9" t="s">
+      <c r="C271" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D271" s="7" t="s">
+      <c r="D271" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E271" s="8"/>
+      <c r="E271" s="7"/>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
         <v>846</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C272" s="9" t="s">
+      <c r="C272" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D272" s="7" t="s">
+      <c r="D272" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E272" s="8"/>
+      <c r="E272" s="7"/>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" t="s">
         <v>847</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C273" s="9" t="s">
+      <c r="C273" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="D273" s="7" t="s">
+      <c r="D273" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E273" s="8"/>
+      <c r="E273" s="7"/>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
         <v>848</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C274" s="9" t="s">
+      <c r="C274" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D274" s="7" t="s">
+      <c r="D274" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E274" s="8"/>
+      <c r="E274" s="7"/>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" t="s">
         <v>849</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C275" s="9" t="s">
+      <c r="C275" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D275" s="7" t="s">
+      <c r="D275" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E275" s="8"/>
+      <c r="E275" s="7"/>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
         <v>850</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C276" s="9" t="s">
+      <c r="C276" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D276" s="7" t="s">
+      <c r="D276" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E276" s="8"/>
+      <c r="E276" s="7"/>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
         <v>851</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C277" s="9" t="s">
+      <c r="C277" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D277" s="7" t="s">
+      <c r="D277" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E277" s="11"/>
+      <c r="E277" s="10"/>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
         <v>852</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C278" s="9" t="s">
+      <c r="C278" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D278" s="7" t="s">
+      <c r="D278" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="E278" s="8"/>
+      <c r="E278" s="7"/>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" t="s">
         <v>853</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C279" s="9" t="s">
+      <c r="C279" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D279" s="7" t="s">
+      <c r="D279" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E279" s="8"/>
+      <c r="E279" s="7"/>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" t="s">
         <v>854</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C280" s="9" t="s">
+      <c r="C280" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D280" s="7" t="s">
+      <c r="D280" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="E280" s="8"/>
+      <c r="E280" s="7"/>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>855</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C281" s="9" t="s">
+      <c r="C281" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D281" s="7" t="s">
+      <c r="D281" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E281" s="8"/>
+      <c r="E281" s="7"/>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
         <v>856</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C282" s="9" t="s">
+      <c r="C282" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D282" s="7" t="s">
+      <c r="D282" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E282" s="8"/>
+      <c r="E282" s="7"/>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" t="s">
         <v>857</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C283" s="9" t="s">
+      <c r="C283" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D283" s="7" t="s">
+      <c r="D283" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E283" s="8"/>
+      <c r="E283" s="7"/>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" t="s">
         <v>858</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C284" s="9" t="s">
+      <c r="C284" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D284" s="7" t="s">
+      <c r="D284" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E284" s="8"/>
+      <c r="E284" s="7"/>
     </row>
     <row r="285" spans="1:5">
       <c r="A285" t="s">
         <v>859</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C285" s="9" t="s">
+      <c r="C285" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D285" s="7" t="s">
+      <c r="D285" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E285" s="8"/>
+      <c r="E285" s="7"/>
     </row>
     <row r="286" spans="1:5">
       <c r="A286" t="s">
         <v>860</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C286" s="9" t="s">
+      <c r="C286" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D286" s="7" t="s">
+      <c r="D286" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E286" s="8"/>
+      <c r="E286" s="7"/>
     </row>
     <row r="287" spans="1:5">
       <c r="A287" t="s">
         <v>861</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C287" s="9" t="s">
+      <c r="C287" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D287" s="7" t="s">
+      <c r="D287" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E287" s="8"/>
+      <c r="E287" s="7"/>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" t="s">
         <v>862</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C288" s="9" t="s">
+      <c r="C288" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D288" s="7" t="s">
+      <c r="D288" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E288" s="8"/>
+      <c r="E288" s="7"/>
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
         <v>863</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C289" s="9" t="s">
+      <c r="C289" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D289" s="7" t="s">
+      <c r="D289" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E289" s="8"/>
+      <c r="E289" s="7"/>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" t="s">
         <v>864</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C290" s="9" t="s">
+      <c r="C290" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D290" s="7" t="s">
+      <c r="D290" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E290" s="8"/>
+      <c r="E290" s="7"/>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" t="s">
         <v>865</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C291" s="9" t="s">
+      <c r="C291" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D291" s="7" t="s">
+      <c r="D291" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E291" s="8"/>
+      <c r="E291" s="7"/>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" t="s">
         <v>866</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C292" s="9" t="s">
+      <c r="C292" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D292" s="7" t="s">
+      <c r="D292" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E292" s="8"/>
+      <c r="E292" s="7"/>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
         <v>867</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C293" s="9" t="s">
+      <c r="C293" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D293" s="7" t="s">
+      <c r="D293" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E293" s="8"/>
+      <c r="E293" s="7"/>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" t="s">
         <v>868</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C294" s="9" t="s">
+      <c r="C294" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D294" s="7" t="s">
+      <c r="D294" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E294" s="8"/>
+      <c r="E294" s="7"/>
     </row>
     <row r="295" spans="1:5">
       <c r="A295" t="s">
         <v>869</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C295" s="9" t="s">
+      <c r="C295" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D295" s="7" t="s">
+      <c r="D295" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E295" s="8"/>
+      <c r="E295" s="7"/>
     </row>
     <row r="296" spans="1:5">
       <c r="A296" t="s">
         <v>870</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C296" s="9" t="s">
+      <c r="C296" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D296" s="7" t="s">
+      <c r="D296" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E296" s="8"/>
+      <c r="E296" s="7"/>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" t="s">
         <v>871</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C297" s="12" t="s">
+      <c r="C297" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D297" s="7" t="s">
+      <c r="D297" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E297" s="7" t="s">
+      <c r="E297" s="6" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7711,61 +7714,61 @@
       <c r="A298" t="s">
         <v>872</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C298" s="13" t="s">
+      <c r="C298" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D298" s="7" t="s">
+      <c r="D298" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E298" s="8"/>
+      <c r="E298" s="7"/>
     </row>
     <row r="299" spans="1:5" ht="26.25">
       <c r="A299" t="s">
         <v>873</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C299" s="14" t="s">
+      <c r="C299" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D299" s="7" t="s">
+      <c r="D299" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E299" s="8"/>
+      <c r="E299" s="7"/>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" t="s">
         <v>874</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C300" s="9" t="s">
+      <c r="C300" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D300" s="7" t="s">
+      <c r="D300" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E300" s="8"/>
+      <c r="E300" s="7"/>
     </row>
     <row r="301" spans="1:5" ht="26.25">
       <c r="A301" t="s">
         <v>875</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C301" s="15" t="s">
+      <c r="C301" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D301" s="7" t="s">
+      <c r="D301" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E301" s="7" t="s">
+      <c r="E301" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7773,59 +7776,59 @@
       <c r="A302" t="s">
         <v>876</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C302" s="9" t="s">
+      <c r="C302" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D302" s="11"/>
-      <c r="E302" s="8"/>
+      <c r="D302" s="10"/>
+      <c r="E302" s="7"/>
     </row>
     <row r="303" spans="1:5">
       <c r="A303" t="s">
         <v>877</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B303" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C303" s="9" t="s">
+      <c r="C303" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D303" s="7" t="s">
+      <c r="D303" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E303" s="8"/>
+      <c r="E303" s="7"/>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" t="s">
         <v>878</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B304" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C304" s="9" t="s">
+      <c r="C304" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="D304" s="7" t="s">
+      <c r="D304" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E304" s="8"/>
+      <c r="E304" s="7"/>
     </row>
     <row r="305" spans="1:5">
       <c r="A305" t="s">
         <v>879</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C305" s="9" t="s">
+      <c r="C305" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D305" s="7" t="s">
+      <c r="D305" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E305" s="16" t="s">
+      <c r="E305" s="15" t="s">
         <v>280</v>
       </c>
     </row>
@@ -7833,217 +7836,217 @@
       <c r="A306" t="s">
         <v>880</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C306" s="9" t="s">
+      <c r="C306" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D306" s="7" t="s">
+      <c r="D306" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E306" s="8"/>
+      <c r="E306" s="7"/>
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
         <v>881</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C307" s="9" t="s">
+      <c r="C307" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D307" s="7" t="s">
+      <c r="D307" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="E307" s="8"/>
+      <c r="E307" s="7"/>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
         <v>882</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C308" s="9" t="s">
+      <c r="C308" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D308" s="7" t="s">
+      <c r="D308" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E308" s="8"/>
+      <c r="E308" s="7"/>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
         <v>883</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C309" s="9" t="s">
+      <c r="C309" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D309" s="7" t="s">
+      <c r="D309" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E309" s="8"/>
+      <c r="E309" s="7"/>
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
         <v>884</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C310" s="9" t="s">
+      <c r="C310" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D310" s="7" t="s">
+      <c r="D310" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E310" s="8"/>
+      <c r="E310" s="7"/>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
         <v>885</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C311" s="9" t="s">
+      <c r="C311" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="D311" s="7" t="s">
+      <c r="D311" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E311" s="8"/>
+      <c r="E311" s="7"/>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
         <v>886</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C312" s="9" t="s">
+      <c r="C312" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D312" s="7" t="s">
+      <c r="D312" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="E312" s="8"/>
+      <c r="E312" s="7"/>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
         <v>887</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C313" s="17" t="s">
+      <c r="C313" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="D313" s="7" t="s">
+      <c r="D313" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="E313" s="8"/>
+      <c r="E313" s="7"/>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
         <v>888</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C314" s="17" t="s">
+      <c r="C314" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="D314" s="7" t="s">
+      <c r="D314" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E314" s="8"/>
+      <c r="E314" s="7"/>
     </row>
     <row r="315" spans="1:5">
       <c r="A315" t="s">
         <v>889</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C315" s="17" t="s">
+      <c r="C315" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="D315" s="7" t="s">
+      <c r="D315" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E315" s="8"/>
+      <c r="E315" s="7"/>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
         <v>890</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C316" s="17" t="s">
+      <c r="C316" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="D316" s="7" t="s">
+      <c r="D316" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E316" s="8"/>
+      <c r="E316" s="7"/>
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
         <v>891</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C317" s="17" t="s">
+      <c r="C317" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D317" s="7" t="s">
+      <c r="D317" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E317" s="8"/>
+      <c r="E317" s="7"/>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
         <v>892</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C318" s="9" t="s">
+      <c r="C318" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D318" s="7" t="s">
+      <c r="D318" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E318" s="8"/>
+      <c r="E318" s="7"/>
     </row>
     <row r="319" spans="1:5">
       <c r="A319" t="s">
         <v>893</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C319" s="17" t="s">
+      <c r="C319" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D319" s="7" t="s">
+      <c r="D319" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E319" s="8"/>
+      <c r="E319" s="7"/>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
         <v>894</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C320" s="2" t="s">
@@ -8058,7 +8061,7 @@
       <c r="A321" t="s">
         <v>895</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B321" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C321" s="2" t="s">
